--- a/data/example-data-wrong.xlsx
+++ b/data/example-data-wrong.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonella\Desktop\bbdataeng\a-small-fhir\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antocruo/Desktop/a-small-fire/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905D6F3F-F52F-4A41-A83E-81F81AE04BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1523A0C-2B66-9A4E-A03D-3A1254D8CE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7903CEA5-AA7C-44DF-9DC5-0F9048285697}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="20740" windowHeight="11040" xr2:uid="{7903CEA5-AA7C-44DF-9DC5-0F9048285697}"/>
   </bookViews>
   <sheets>
     <sheet name="Book1" sheetId="1" r:id="rId1"/>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>PATIENT_ID</t>
   </si>
   <si>
-    <t>ICD-10</t>
-  </si>
-  <si>
     <t>DONOR_AGE</t>
   </si>
   <si>
@@ -71,18 +68,12 @@
     <t>C18.9</t>
   </si>
   <si>
-    <t>DOB</t>
-  </si>
-  <si>
     <t>MATERIAL_TYPE</t>
   </si>
   <si>
     <t>DIAGNOSIS_DATE</t>
   </si>
   <si>
-    <t>STORAGE_TEMP</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
@@ -92,28 +83,34 @@
     <t>Tessuto</t>
   </si>
   <si>
-    <t>DIAGNOSIS_AGE</t>
-  </si>
-  <si>
     <t>C18,2</t>
   </si>
   <si>
     <t>k colon</t>
   </si>
   <si>
-    <t>Room</t>
-  </si>
-  <si>
-    <t>-60to-85</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>TissueFFPE</t>
-  </si>
-  <si>
-    <t>TissueFrozen</t>
+    <t>DIAGNOSIS</t>
+  </si>
+  <si>
+    <t>STORAGE_TEMPERATURE</t>
+  </si>
+  <si>
+    <t>Tissue (frozen)</t>
+  </si>
+  <si>
+    <t>Tissue (paraffin preserved)</t>
+  </si>
+  <si>
+    <t>-60°C to -80°C</t>
+  </si>
+  <si>
+    <t>BIRTH_DATE</t>
+  </si>
+  <si>
+    <t>DIAGNOSIS_DONOR_AGE</t>
+  </si>
+  <si>
+    <t>Room Temperature</t>
   </si>
 </sst>
 </file>
@@ -132,6 +129,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -211,9 +209,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -223,9 +218,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -241,7 +239,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -558,59 +556,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB8A45B-4F8B-45BC-A272-7D87119AF989}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="4">
         <v>43960</v>
@@ -625,24 +623,24 @@
         <v>80</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="4">
         <v>43960</v>
@@ -657,24 +655,22 @@
         <v>82</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>21</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="C4" s="4">
         <v>43960</v>
@@ -689,16 +685,16 @@
         <v>80</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
